--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$194</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5908" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6303" uniqueCount="808">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>Dieses Profil beschreibt die zielgerichtete Mikroskopie, bei der das gesuchte Objekt und die Färbetechnik im Untersuchungscode stehen und das Ergebnis die Menge des Gesehenen ist.</t>
+    <t>Dieses Profil beschreibt die zielgerichtete Mikroskopie, bei der das gesuchte Objekt im Untersuchungscode steht und das Ergebnis der Nachweis oder Ausschluss dieses Objekts ist; wie viel davon gesehen wurde, steht in der Mengenkomponente.</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -1672,823 +1672,891 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
+    <t>Messwert</t>
+  </si>
+  <si>
+    <t>Wert der Analyse</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>ele-1
+obs-7</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Nachweis oder Ausschluss des im Code benannten Objekts. Die Menge des Gesehenen gehoert NICHT hierher, sondern in component[menge]. Liefert die Untersuchung gar keine verwertbare Aussage, dataAbsentReason.</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-detected-not-detected-snomed</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.version</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.display</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.value[x].text</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.extension:pqTranslation</t>
+  </si>
+  <si>
+    <t>pqTranslation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {extension-quantity-translation}
+</t>
+  </si>
+  <si>
+    <t>Same quantity with different units</t>
+  </si>
+  <si>
+    <t>An alternative representation of the same physical quantity expressed in a different unit from a different unit code system and possibly with a different value.</t>
+  </si>
+  <si>
+    <t>It is not necessary for information processing entities to check and enforce that the translations are valid translations of the base unit, but they are allowed to do so, and to reject instances where the translations are not valid. 
+NOTE Translations are allowed to contain other representations in UCUM units, but there is generally no point to this as it is possible to convert from one UCUM form to another.</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value.extension:quantityPrecision</t>
+  </si>
+  <si>
+    <t>quantityPrecision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {quantity-precision}
+</t>
+  </si>
+  <si>
+    <t>Explicit precision (number of significant decimal places)</t>
+  </si>
+  <si>
+    <t>Explicit precision of the number. This is the number of significant decimal places after the decimal point, irrespective of how many are actually present in the explicitly represented decimal.</t>
+  </si>
+  <si>
+    <t>The presence of this extension does not change conformance expectations with regard to rendering and calculations that use the number - these are still based on the raw decimal value. Applications that perform calculations SHALL ensure that this extension is removed or updated to the correct precision value if the number is changed. Applications should consider using the exponential form (e.g. 2.10e3) on the raw decimal to manage significant figures, but should be mindful of human display when doing so.</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.value.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x].value.value</t>
+  </si>
+  <si>
+    <t>Primitive value for decimal</t>
+  </si>
+  <si>
+    <t>decimal.value</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.comparator</t>
+  </si>
+  <si>
+    <t>Observation.value[x].comparator</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.system</t>
+  </si>
+  <si>
+    <t>Observation.value[x].system</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>http://unitsofmeasure.org</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t>ele-1
+qty-3</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The mandatory system is UCUM.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRange</t>
+  </si>
+  <si>
+    <t>valueRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueRatio</t>
+  </si>
+  <si>
+    <t>valueRatio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>Observation.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Grund für fehlende Daten</t>
+  </si>
+  <si>
+    <t>unbekannt | maskiert | nicht anwendbar | Fehler | nicht durchgeführt</t>
+  </si>
+  <si>
+    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
+  </si>
+  <si>
+    <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-data-absent-reason</t>
+  </si>
+  <si>
+    <t>ele-1
+obs-6</t>
+  </si>
+  <si>
+    <t>Observation.interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abnormal Flag
+</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>Eine kategorische Bewertung des Messwertes. Zum Beispiel hoch, niedrig, normal.</t>
+  </si>
+  <si>
+    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollständige ValueSet Observation Interpretation Codes; das Modul schränkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible ist, dürfen darüber hinaus weitere Codes verwendet werden; praktisch relevant sind die abnormal-Codes HH, LL und AA, etwa für Werte jenseits der Telefongrenze.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>
+  </si>
+  <si>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Hinweis</t>
+  </si>
+  <si>
+    <t>Zusätzliche Informationen zur Laboruntersuchung als Freitext.</t>
+  </si>
+  <si>
+    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
+  </si>
+  <si>
+    <t>Need to be able to provide free text additional information.</t>
+  </si>
+  <si>
+    <t>Observation.bodySite</t>
+  </si>
+  <si>
+    <t>Observed body part</t>
+  </si>
+  <si>
+    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>Das mikroskopische Verfahren. Die Faerbung gehoert NICHT hierher, sondern in extension[faerbung].</t>
+  </si>
+  <si>
+    <t>Konkrete Untersuchungsmethode, wenn der verwendete LOINC-Code für den Laborparameter keine Methode enthält.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code for Observation.code.</t>
+  </si>
+  <si>
+    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-morphologie-methode-snomed</t>
+  </si>
+  <si>
+    <t>Observation.method.id</t>
+  </si>
+  <si>
+    <t>Observation.method.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.method.text</t>
+  </si>
+  <si>
+    <t>Observation.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
+</t>
+  </si>
+  <si>
+    <t>Probenmaterial</t>
+  </si>
+  <si>
+    <t>Probe, auf deren Basis die Laboruntersuchungen angefertigt werden</t>
+  </si>
+  <si>
+    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>Observation.specimen.id</t>
+  </si>
+  <si>
+    <t>Observation.specimen.extension</t>
+  </si>
+  <si>
+    <t>Observation.specimen.reference</t>
+  </si>
+  <si>
+    <t>Observation.specimen.type</t>
+  </si>
+  <si>
+    <t>Observation.specimen.identifier</t>
+  </si>
+  <si>
+    <t>Observation.specimen.display</t>
+  </si>
+  <si>
+    <t>Observation.device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
+</t>
+  </si>
+  <si>
+    <t>Gerät</t>
+  </si>
+  <si>
+    <t>Gerät, das zur Generierung der Messwerte verwendet wurde.</t>
+  </si>
+  <si>
+    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
+  </si>
+  <si>
+    <t>Observation.device.id</t>
+  </si>
+  <si>
+    <t>Observation.device.extension</t>
+  </si>
+  <si>
+    <t>Observation.device.reference</t>
+  </si>
+  <si>
+    <t>Observation.device.type</t>
+  </si>
+  <si>
+    <t>Observation.device.identifier</t>
+  </si>
+  <si>
+    <t>Observation.device.display</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Referenzbereich</t>
+  </si>
+  <si>
+    <t>Bereich, in dem der Messwert als normal oder empfohlen betrachtet wird.</t>
+  </si>
+  <si>
+    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
+  </si>
+  <si>
+    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.id</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.extension</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity}
+</t>
+  </si>
+  <si>
+    <t>Low Range, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
+  </si>
+  <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1
+obs-3</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.high</t>
+  </si>
+  <si>
+    <t>High Range, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.type</t>
+  </si>
+  <si>
+    <t>Reference range qualifier</t>
+  </si>
+  <si>
+    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
+  </si>
+  <si>
+    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
+  </si>
+  <si>
+    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
+  </si>
+  <si>
+    <t>Code for the meaning of a reference range.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.appliesTo</t>
+  </si>
+  <si>
+    <t>Reference range population</t>
+  </si>
+  <si>
+    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
+  </si>
+  <si>
+    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
+  </si>
+  <si>
+    <t>Need to be able to identify the target population for proper interpretation.</t>
+  </si>
+  <si>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.age</t>
+  </si>
+  <si>
+    <t>Applicable age range, if relevant</t>
+  </si>
+  <si>
+    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
+  </si>
+  <si>
+    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
+  </si>
+  <si>
+    <t>Some analytes vary greatly over age.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.text</t>
+  </si>
+  <si>
+    <t>Text based reference range in an observation</t>
+  </si>
+  <si>
+    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
+  </si>
+  <si>
+    <t>Observation.hasMember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+</t>
+  </si>
+  <si>
+    <t>Related resource that belongs to the Observation group</t>
+  </si>
+  <si>
+    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+  </si>
+  <si>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+  </si>
+  <si>
+    <t>Observation.derivedFrom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+</t>
+  </si>
+  <si>
+    <t>Related measurements the observation is made from</t>
+  </si>
+  <si>
+    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+  </si>
+  <si>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+  </si>
+  <si>
+    <t>Observation.component</t>
+  </si>
+  <si>
+    <t>Component results</t>
+  </si>
+  <si>
+    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
+  </si>
+  <si>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this.code}
+</t>
+  </si>
+  <si>
+    <t>Slicing nach dem Komponenten-Code.</t>
+  </si>
+  <si>
+    <t>Observation.component.id</t>
+  </si>
+  <si>
+    <t>Observation.component.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component.code</t>
+  </si>
+  <si>
+    <t>Type of component observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
+  </si>
+  <si>
+    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+  </si>
+  <si>
+    <t>Actual component result</t>
+  </si>
+  <si>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>Observation.component.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the component result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
+  </si>
+  <si>
+    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+  </si>
+  <si>
+    <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation of component result</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:menge</t>
+  </si>
+  <si>
+    <t>menge</t>
+  </si>
+  <si>
+    <t>Semiquantitative Menge oder Zaehlung des berichteten Befunds</t>
+  </si>
+  <si>
+    <t>Wie viel des Befunds gesehen wurde: als semiquantitative Stufe, als Zaehlung je Gesichtsfeld oder als Intervall einer solchen Zaehlung.</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.id</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+    &lt;code value="103392008"/&gt;
+    &lt;display value="Semi-quantitative value"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]</t>
+  </si>
+  <si>
     <t>Quantity
 CodeableConceptRange</t>
   </si>
   <si>
-    <t>Messwert</t>
-  </si>
-  <si>
-    <t>Wert der Analyse</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-7</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
+    <t>Observation.component:menge.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Semiquantitative Stufe, z. B. 'Few' oder 'Present two plus out of three plus'.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity</t>
   </si>
   <si>
     <t>Zaehlung je Gesichtsfeld, UCUM-Einheit /[HPF]. Fuer offene Grenzen wird Quantity.comparator verwendet, z. B. '&lt;10/GF' als comparator = '&lt;', value = 10.</t>
   </si>
   <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.extension:pqTranslation</t>
-  </si>
-  <si>
-    <t>pqTranslation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {extension-quantity-translation}
-</t>
-  </si>
-  <si>
-    <t>Same quantity with different units</t>
-  </si>
-  <si>
-    <t>An alternative representation of the same physical quantity expressed in a different unit from a different unit code system and possibly with a different value.</t>
-  </si>
-  <si>
-    <t>It is not necessary for information processing entities to check and enforce that the translations are valid translations of the base unit, but they are allowed to do so, and to reject instances where the translations are not valid. 
-NOTE Translations are allowed to contain other representations in UCUM units, but there is generally no point to this as it is possible to convert from one UCUM form to another.</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.value.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.value.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.value.extension:quantityPrecision</t>
-  </si>
-  <si>
-    <t>quantityPrecision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {quantity-precision}
-</t>
-  </si>
-  <si>
-    <t>Explicit precision (number of significant decimal places)</t>
-  </si>
-  <si>
-    <t>Explicit precision of the number. This is the number of significant decimal places after the decimal point, irrespective of how many are actually present in the explicitly represented decimal.</t>
-  </si>
-  <si>
-    <t>The presence of this extension does not change conformance expectations with regard to rendering and calculations that use the number - these are still based on the raw decimal value. Applications that perform calculations SHALL ensure that this extension is removed or updated to the correct precision value if the number is changed. Applications should consider using the exponential form (e.g. 2.10e3) on the raw decimal to manage significant figures, but should be mindful of human display when doing so.</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.value.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value.value</t>
-  </si>
-  <si>
-    <t>Primitive value for decimal</t>
-  </si>
-  <si>
-    <t>decimal.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>http://unitsofmeasure.org</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t>ele-1
-qty-3</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The mandatory system is UCUM.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Semiquantitative Stufe des im Code benannten Objekts. Weil der Untersuchungscode ordinal ist, ist die Stufe der Wert — nicht die Interpretation und keine Komponente. Wurde untersucht und nichts gesehen, wird 'None' oder 'No organisms seen' berichtet; liefert die Untersuchung gar keine verwertbare Aussage, dataAbsentReason.</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.version</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.value[x].text</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueRange</t>
-  </si>
-  <si>
-    <t>valueRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
+    <t>Observation.component:menge.value[x]:valueRange</t>
   </si>
   <si>
     <t>Zaehlung je Gesichtsfeld als Intervall, UCUM-Einheit /[HPF] — z. B. '10-25/GF' als low = 10, high = 25.</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueRatio</t>
-  </si>
-  <si>
-    <t>valueRatio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio
-</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Grund für fehlende Daten</t>
-  </si>
-  <si>
-    <t>unbekannt | maskiert | nicht anwendbar | Fehler | nicht durchgeführt</t>
-  </si>
-  <si>
-    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
-  </si>
-  <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-data-absent-reason</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-6</t>
-  </si>
-  <si>
-    <t>Observation.interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abnormal Flag
-</t>
-  </si>
-  <si>
-    <t>Interpretation</t>
-  </si>
-  <si>
-    <t>Eine kategorische Bewertung des Messwertes. Zum Beispiel hoch, niedrig, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
-  </si>
-  <si>
-    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollständige ValueSet Observation Interpretation Codes; das Modul schränkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible ist, dürfen darüber hinaus weitere Codes verwendet werden; praktisch relevant sind die abnormal-Codes HH, LL und AA, etwa für Werte jenseits der Telefongrenze.</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>
-  </si>
-  <si>
-    <t>Observation.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Hinweis</t>
-  </si>
-  <si>
-    <t>Zusätzliche Informationen zur Laboruntersuchung als Freitext.</t>
-  </si>
-  <si>
-    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
-  </si>
-  <si>
-    <t>Need to be able to provide free text additional information.</t>
-  </si>
-  <si>
-    <t>Observation.bodySite</t>
-  </si>
-  <si>
-    <t>Observed body part</t>
-  </si>
-  <si>
-    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
-  </si>
-  <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>Das mikroskopische Verfahren. Die Faerbung gehoert NICHT hierher, sondern in extension[faerbung].</t>
-  </si>
-  <si>
-    <t>Konkrete Untersuchungsmethode, wenn der verwendete LOINC-Code für den Laborparameter keine Methode enthält.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-morphologie-methode-snomed</t>
-  </si>
-  <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
-  </si>
-  <si>
-    <t>Observation.specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
-</t>
-  </si>
-  <si>
-    <t>Probenmaterial</t>
-  </si>
-  <si>
-    <t>Probe, auf deren Basis die Laboruntersuchungen angefertigt werden</t>
-  </si>
-  <si>
-    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
-  </si>
-  <si>
-    <t>Observation.specimen.id</t>
-  </si>
-  <si>
-    <t>Observation.specimen.extension</t>
-  </si>
-  <si>
-    <t>Observation.specimen.reference</t>
-  </si>
-  <si>
-    <t>Observation.specimen.type</t>
-  </si>
-  <si>
-    <t>Observation.specimen.identifier</t>
-  </si>
-  <si>
-    <t>Observation.specimen.display</t>
-  </si>
-  <si>
-    <t>Observation.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
-</t>
-  </si>
-  <si>
-    <t>Gerät</t>
-  </si>
-  <si>
-    <t>Gerät, das zur Generierung der Messwerte verwendet wurde.</t>
-  </si>
-  <si>
-    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
-  </si>
-  <si>
-    <t>Observation.device.id</t>
-  </si>
-  <si>
-    <t>Observation.device.extension</t>
-  </si>
-  <si>
-    <t>Observation.device.reference</t>
-  </si>
-  <si>
-    <t>Observation.device.type</t>
-  </si>
-  <si>
-    <t>Observation.device.identifier</t>
-  </si>
-  <si>
-    <t>Observation.device.display</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Referenzbereich</t>
-  </si>
-  <si>
-    <t>Bereich, in dem der Messwert als normal oder empfohlen betrachtet wird.</t>
-  </si>
-  <si>
-    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
-</t>
-  </si>
-  <si>
-    <t>Low Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
-  </si>
-  <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1
-obs-3</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high</t>
-  </si>
-  <si>
-    <t>High Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.type</t>
-  </si>
-  <si>
-    <t>Reference range qualifier</t>
-  </si>
-  <si>
-    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Code for the meaning of a reference range.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo</t>
-  </si>
-  <si>
-    <t>Reference range population</t>
-  </si>
-  <si>
-    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Codes identifying the population the reference range applies to.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t>Applicable age range, if relevant</t>
-  </si>
-  <si>
-    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
-  </si>
-  <si>
-    <t>The stated low and high value are assumed to have arbitrarily high precision when it comes to determining which values are in the range. I.e. 1.99 is not in the range 2 -&gt; 3.</t>
-  </si>
-  <si>
-    <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-rng-2:If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.text</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
-  </si>
-  <si>
-    <t>Observation.hasMember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
-</t>
-  </si>
-  <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
-  </si>
-  <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
-  </si>
-  <si>
-    <t>Observation.derivedFrom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
-</t>
-  </si>
-  <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
-  </si>
-  <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
-  </si>
-  <si>
-    <t>Observation.component</t>
-  </si>
-  <si>
-    <t>Component results</t>
-  </si>
-  <si>
-    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
-  </si>
-  <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t>Observation.component.id</t>
-  </si>
-  <si>
-    <t>Observation.component.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component.code</t>
-  </si>
-  <si>
-    <t>Type of component observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
-  </si>
-  <si>
-    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]</t>
-  </si>
-  <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
-  </si>
-  <si>
-    <t>Actual component result</t>
-  </si>
-  <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>Observation.component.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the component result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.component.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>"Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
-  </si>
-  <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
-  </si>
-  <si>
-    <t>Observation.component.interpretation</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
-  </si>
-  <si>
-    <t>Observation.component.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation of component result</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+    <t>Observation.component:menge.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2809,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ182"/>
+  <dimension ref="A1:AJ194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -13413,19 +13481,19 @@
         <v>85</v>
       </c>
       <c r="K104" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="L104" t="s" s="2">
+      <c r="M104" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -13462,14 +13530,14 @@
         <v>77</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>524</v>
@@ -13481,7 +13549,7 @@
         <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>92</v>
@@ -13489,13 +13557,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>524</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>77</v>
@@ -13517,19 +13585,19 @@
         <v>85</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L105" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="N105" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O105" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -13554,13 +13622,11 @@
         <v>77</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>77</v>
+        <v>536</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>77</v>
@@ -13587,7 +13653,7 @@
         <v>84</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>92</v>
@@ -13595,10 +13661,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13695,10 +13761,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13795,48 +13861,48 @@
         <v>113</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="B108" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>543</v>
-      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>544</v>
+        <v>138</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>545</v>
+        <v>302</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>546</v>
+        <v>303</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
       </c>
@@ -13884,7 +13950,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>112</v>
+        <v>307</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -13896,15 +13962,15 @@
         <v>91</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13912,35 +13978,31 @@
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>550</v>
+        <v>99</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>551</v>
+        <v>100</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
       </c>
@@ -13988,7 +14050,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>555</v>
+        <v>102</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -13997,29 +14059,29 @@
         <v>84</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>77</v>
@@ -14031,15 +14093,17 @@
         <v>77</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14076,73 +14140,75 @@
         <v>77</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>106</v>
+        <v>316</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>107</v>
+        <v>317</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="O111" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
       </c>
@@ -14178,45 +14244,43 @@
         <v>77</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>112</v>
+        <v>321</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="C112" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -14232,19 +14296,19 @@
         <v>77</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>562</v>
+        <v>99</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>563</v>
+        <v>324</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>564</v>
+        <v>325</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>565</v>
+        <v>326</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14294,27 +14358,27 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>112</v>
+        <v>327</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14322,31 +14386,35 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>550</v>
+        <v>160</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>568</v>
+        <v>330</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
       </c>
@@ -14394,7 +14462,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>569</v>
+        <v>335</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14403,18 +14471,18 @@
         <v>84</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14428,35 +14496,33 @@
         <v>84</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="J114" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>572</v>
+        <v>338</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>573</v>
+        <v>339</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>332</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>574</v>
+        <v>340</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q114" t="s" s="2">
-        <v>575</v>
-      </c>
+      <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
         <v>77</v>
       </c>
@@ -14476,13 +14542,13 @@
         <v>77</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>576</v>
+        <v>77</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>577</v>
+        <v>77</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>77</v>
@@ -14500,7 +14566,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>578</v>
+        <v>341</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
@@ -14515,12 +14581,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14528,13 +14594,13 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>77</v>
@@ -14543,19 +14609,19 @@
         <v>85</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>99</v>
+        <v>344</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>581</v>
+        <v>345</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>582</v>
+        <v>346</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>583</v>
+        <v>348</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -14604,7 +14670,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>584</v>
+        <v>349</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -14619,12 +14685,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>585</v>
+        <v>557</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>586</v>
+        <v>558</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14632,13 +14698,13 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>77</v>
@@ -14647,26 +14713,26 @@
         <v>85</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>587</v>
+        <v>352</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>588</v>
+        <v>353</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>589</v>
+        <v>354</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>590</v>
+        <v>355</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
-        <v>591</v>
+        <v>77</v>
       </c>
       <c r="S116" t="s" s="2">
         <v>77</v>
@@ -14708,7 +14774,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>592</v>
+        <v>356</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -14717,7 +14783,7 @@
         <v>84</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>593</v>
+        <v>91</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>92</v>
@@ -14725,18 +14791,20 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>594</v>
+        <v>559</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>84</v>
@@ -14751,19 +14819,19 @@
         <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>160</v>
+        <v>561</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>597</v>
+        <v>535</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>598</v>
+        <v>527</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>599</v>
+        <v>528</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -14812,7 +14880,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>600</v>
+        <v>524</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
@@ -14821,22 +14889,20 @@
         <v>84</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>91</v>
+        <v>531</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>601</v>
+        <v>563</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>77</v>
       </c>
@@ -14848,29 +14914,25 @@
         <v>84</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>287</v>
+        <v>99</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>603</v>
+        <v>100</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>77</v>
       </c>
@@ -14894,11 +14956,13 @@
         <v>77</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="Y118" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z118" t="s" s="2">
-        <v>604</v>
+        <v>77</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>77</v>
@@ -14916,7 +14980,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>524</v>
+        <v>102</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>75</v>
@@ -14925,29 +14989,29 @@
         <v>84</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>532</v>
+        <v>77</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>605</v>
+        <v>564</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>77</v>
@@ -14959,15 +15023,17 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15004,41 +15070,43 @@
         <v>77</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>606</v>
+        <v>565</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="C120" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="D120" t="s" s="2">
         <v>104</v>
       </c>
@@ -15059,16 +15127,16 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>105</v>
+        <v>567</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>106</v>
+        <v>568</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>107</v>
+        <v>569</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>108</v>
+        <v>570</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15106,16 +15174,16 @@
         <v>77</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
         <v>112</v>
@@ -15135,10 +15203,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>607</v>
+        <v>571</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>608</v>
+        <v>572</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15149,7 +15217,7 @@
         <v>84</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>85</v>
@@ -15161,19 +15229,19 @@
         <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>138</v>
+        <v>573</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>302</v>
+        <v>574</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>303</v>
+        <v>575</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>304</v>
+        <v>576</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>305</v>
+        <v>577</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>77</v>
@@ -15222,13 +15290,13 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>307</v>
+        <v>578</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>91</v>
@@ -15239,10 +15307,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>609</v>
+        <v>579</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15339,10 +15407,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>611</v>
+        <v>581</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>612</v>
+        <v>582</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15441,18 +15509,20 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>613</v>
+        <v>583</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="D124" t="s" s="2">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>84</v>
@@ -15464,23 +15534,21 @@
         <v>77</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>126</v>
+        <v>585</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>316</v>
+        <v>586</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>317</v>
+        <v>587</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>77</v>
       </c>
@@ -15528,27 +15596,27 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>321</v>
+        <v>112</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>92</v>
+        <v>113</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>616</v>
+        <v>590</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15562,26 +15630,24 @@
         <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>99</v>
+        <v>573</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>324</v>
+        <v>591</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -15630,7 +15696,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>327</v>
+        <v>592</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>75</v>
@@ -15639,18 +15705,18 @@
         <v>84</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15658,7 +15724,7 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G126" t="s" s="2">
         <v>84</v>
@@ -15667,7 +15733,7 @@
         <v>85</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J126" t="s" s="2">
         <v>85</v>
@@ -15676,21 +15742,23 @@
         <v>160</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>330</v>
+        <v>595</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>331</v>
+        <v>596</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>332</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>333</v>
+        <v>597</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q126" s="2"/>
+      <c r="Q126" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="R126" t="s" s="2">
         <v>77</v>
       </c>
@@ -15710,13 +15778,13 @@
         <v>77</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>77</v>
+        <v>599</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>77</v>
+        <v>600</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>77</v>
@@ -15734,7 +15802,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>335</v>
+        <v>601</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>75</v>
@@ -15749,12 +15817,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15762,13 +15830,13 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>77</v>
@@ -15780,16 +15848,16 @@
         <v>99</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>338</v>
+        <v>604</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>339</v>
+        <v>605</v>
       </c>
       <c r="N127" t="s" s="2">
         <v>332</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>340</v>
+        <v>606</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -15838,7 +15906,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>341</v>
+        <v>607</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>75</v>
@@ -15853,12 +15921,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15866,13 +15934,13 @@
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>77</v>
@@ -15881,26 +15949,26 @@
         <v>85</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>344</v>
+        <v>126</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>345</v>
+        <v>610</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>346</v>
+        <v>611</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>347</v>
+        <v>612</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>348</v>
+        <v>613</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>77</v>
+        <v>614</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>77</v>
@@ -15942,7 +16010,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>349</v>
+        <v>615</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -15951,18 +16019,18 @@
         <v>84</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>91</v>
+        <v>616</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15970,13 +16038,13 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>77</v>
@@ -15985,19 +16053,19 @@
         <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>352</v>
+        <v>619</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>353</v>
+        <v>620</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>354</v>
+        <v>621</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>355</v>
+        <v>622</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -16046,7 +16114,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>356</v>
+        <v>623</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -16063,13 +16131,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>524</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>77</v>
@@ -16091,19 +16159,19 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>628</v>
+        <v>562</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N130" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -16161,7 +16229,7 @@
         <v>84</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>92</v>
@@ -16169,13 +16237,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>524</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>77</v>
@@ -16197,19 +16265,19 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>632</v>
+        <v>562</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="N131" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O131" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -16267,7 +16335,7 @@
         <v>84</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AJ131" t="s" s="2">
         <v>92</v>
@@ -16275,10 +16343,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -16304,16 +16372,16 @@
         <v>287</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O132" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -16342,7 +16410,7 @@
       </c>
       <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>77</v>
@@ -16360,7 +16428,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>75</v>
@@ -16369,7 +16437,7 @@
         <v>84</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>92</v>
@@ -16377,14 +16445,14 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -16406,16 +16474,16 @@
         <v>287</v>
       </c>
       <c r="L133" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O133" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -16443,10 +16511,10 @@
         <v>142</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>77</v>
@@ -16464,7 +16532,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>75</v>
@@ -16481,10 +16549,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16507,19 +16575,19 @@
         <v>77</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N134" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -16568,7 +16636,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>75</v>
@@ -16585,10 +16653,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16614,13 +16682,13 @@
         <v>287</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -16649,10 +16717,10 @@
         <v>150</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -16670,7 +16738,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>75</v>
@@ -16687,10 +16755,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16716,16 +16784,16 @@
         <v>287</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O136" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>77</v>
@@ -16754,7 +16822,7 @@
       </c>
       <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>77</v>
@@ -16772,7 +16840,7 @@
         <v>77</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>75</v>
@@ -16789,10 +16857,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16889,10 +16957,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16991,10 +17059,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17095,10 +17163,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17195,10 +17263,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -17297,10 +17365,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -17401,10 +17469,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17503,10 +17571,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17607,10 +17675,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17711,10 +17779,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17815,10 +17883,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17919,10 +17987,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17945,16 +18013,16 @@
         <v>77</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -18004,7 +18072,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -18021,10 +18089,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -18121,10 +18189,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -18223,10 +18291,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -18325,10 +18393,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18427,10 +18495,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18529,10 +18597,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18631,10 +18699,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18657,16 +18725,16 @@
         <v>77</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="N155" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="L155" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -18716,7 +18784,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>75</v>
@@ -18733,10 +18801,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18833,10 +18901,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18935,10 +19003,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -19037,10 +19105,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -19139,10 +19207,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -19241,10 +19309,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -19343,10 +19411,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19369,19 +19437,19 @@
         <v>77</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L162" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="M162" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="N162" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>701</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -19430,7 +19498,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>75</v>
@@ -19442,15 +19510,15 @@
         <v>91</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19547,10 +19615,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19649,14 +19717,14 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
@@ -19678,10 +19746,10 @@
         <v>105</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>108</v>
@@ -19736,7 +19804,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>75</v>
@@ -19753,10 +19821,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19779,16 +19847,16 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="L166" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -19838,7 +19906,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>75</v>
@@ -19847,18 +19915,18 @@
         <v>84</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19881,16 +19949,16 @@
         <v>77</v>
       </c>
       <c r="K167" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="L167" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>717</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -19940,7 +20008,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>75</v>
@@ -19949,18 +20017,18 @@
         <v>84</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19986,16 +20054,16 @@
         <v>287</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="O168" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>727</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -20023,10 +20091,10 @@
         <v>164</v>
       </c>
       <c r="Y168" t="s" s="2">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="Z168" t="s" s="2">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>77</v>
@@ -20044,7 +20112,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>75</v>
@@ -20061,10 +20129,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -20090,16 +20158,16 @@
         <v>287</v>
       </c>
       <c r="L169" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>730</v>
+      </c>
+      <c r="O169" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="M169" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -20127,10 +20195,10 @@
         <v>150</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>77</v>
@@ -20148,7 +20216,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>75</v>
@@ -20165,10 +20233,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -20191,19 +20259,19 @@
         <v>77</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L170" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="O170" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="M170" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="O170" t="s" s="2">
-        <v>741</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -20252,7 +20320,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>75</v>
@@ -20264,15 +20332,15 @@
         <v>91</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20298,10 +20366,10 @@
         <v>99</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>332</v>
@@ -20354,7 +20422,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>75</v>
@@ -20371,10 +20439,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20397,16 +20465,16 @@
         <v>85</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>747</v>
-      </c>
-      <c r="L172" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -20456,7 +20524,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>75</v>
@@ -20473,10 +20541,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20499,16 +20567,16 @@
         <v>85</v>
       </c>
       <c r="K173" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N173" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="L173" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="M173" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>755</v>
       </c>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
@@ -20558,7 +20626,7 @@
         <v>77</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -20575,10 +20643,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20601,19 +20669,19 @@
         <v>85</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="L174" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="O174" t="s" s="2">
         <v>757</v>
-      </c>
-      <c r="M174" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="O174" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>77</v>
@@ -20650,19 +20718,19 @@
         <v>77</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>77</v>
+        <v>758</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>77</v>
+        <v>759</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>75</v>
@@ -20679,10 +20747,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20779,10 +20847,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20881,14 +20949,14 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
@@ -20910,10 +20978,10 @@
         <v>105</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>108</v>
@@ -20968,7 +21036,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>75</v>
@@ -20985,10 +21053,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -21014,13 +21082,13 @@
         <v>287</v>
       </c>
       <c r="L178" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M178" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="M178" t="s" s="2">
+      <c r="N178" t="s" s="2">
         <v>766</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>767</v>
       </c>
       <c r="O178" t="s" s="2">
         <v>430</v>
@@ -21051,11 +21119,11 @@
         <v>150</v>
       </c>
       <c r="Y178" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="Z178" t="s" s="2">
         <v>768</v>
       </c>
-      <c r="Z178" t="s" s="2">
-        <v>769</v>
-      </c>
       <c r="AA178" t="s" s="2">
         <v>77</v>
       </c>
@@ -21072,7 +21140,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>84</v>
@@ -21089,10 +21157,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21115,19 +21183,19 @@
         <v>85</v>
       </c>
       <c r="K179" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="L179" t="s" s="2">
         <v>771</v>
       </c>
-      <c r="L179" t="s" s="2">
+      <c r="M179" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N179" t="s" s="2">
         <v>772</v>
       </c>
-      <c r="M179" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>773</v>
-      </c>
       <c r="O179" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>77</v>
@@ -21176,7 +21244,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -21193,10 +21261,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21222,16 +21290,16 @@
         <v>287</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="M180" t="s" s="2">
         <v>775</v>
       </c>
-      <c r="M180" t="s" s="2">
+      <c r="N180" t="s" s="2">
         <v>776</v>
       </c>
-      <c r="N180" t="s" s="2">
-        <v>777</v>
-      </c>
       <c r="O180" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>77</v>
@@ -21259,11 +21327,11 @@
         <v>142</v>
       </c>
       <c r="Y180" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="Z180" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="Z180" t="s" s="2">
-        <v>779</v>
-      </c>
       <c r="AA180" t="s" s="2">
         <v>77</v>
       </c>
@@ -21280,7 +21348,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
@@ -21289,7 +21357,7 @@
         <v>84</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>92</v>
@@ -21297,14 +21365,14 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
@@ -21326,16 +21394,16 @@
         <v>287</v>
       </c>
       <c r="L181" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M181" t="s" s="2">
         <v>781</v>
       </c>
-      <c r="M181" t="s" s="2">
-        <v>782</v>
-      </c>
       <c r="N181" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>77</v>
@@ -21363,11 +21431,11 @@
         <v>142</v>
       </c>
       <c r="Y181" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z181" t="s" s="2">
         <v>783</v>
       </c>
-      <c r="Z181" t="s" s="2">
-        <v>784</v>
-      </c>
       <c r="AA181" t="s" s="2">
         <v>77</v>
       </c>
@@ -21384,7 +21452,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>
@@ -21401,10 +21469,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -21430,16 +21498,16 @@
         <v>78</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M182" t="s" s="2">
         <v>786</v>
       </c>
-      <c r="M182" t="s" s="2">
-        <v>787</v>
-      </c>
       <c r="N182" t="s" s="2">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>77</v>
@@ -21488,7 +21556,7 @@
         <v>77</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>75</v>
@@ -21503,8 +21571,1254 @@
         <v>77</v>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="C183" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="D183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="P183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q183" s="2"/>
+      <c r="R183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="184" hidden="true">
+      <c r="A184" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="C184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G184" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N184" s="2"/>
+      <c r="O184" s="2"/>
+      <c r="P184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q184" s="2"/>
+      <c r="R184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="185" hidden="true">
+      <c r="A185" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="C185" s="2"/>
+      <c r="D185" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E185" s="2"/>
+      <c r="F185" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K185" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M185" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N185" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O185" s="2"/>
+      <c r="P185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q185" s="2"/>
+      <c r="R185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI185" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ185" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" hidden="true">
+      <c r="A186" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="P186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q186" s="2"/>
+      <c r="R186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="187" hidden="true">
+      <c r="A187" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y187" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="Z187" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="188" hidden="true">
+      <c r="A188" t="s" s="2">
+        <v>796</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J188" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K188" t="s" s="2">
+        <v>797</v>
+      </c>
+      <c r="L188" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O188" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q188" s="2"/>
+      <c r="R188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AC188" s="2"/>
+      <c r="AD188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AF188" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG188" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI188" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ188" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="189" hidden="true">
+      <c r="A189" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="D189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J189" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K189" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q189" s="2"/>
+      <c r="R189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y189" s="2"/>
+      <c r="Z189" t="s" s="2">
+        <v>800</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF189" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG189" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH189" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI189" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ189" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="190" hidden="true">
+      <c r="A190" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="D190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q190" s="2"/>
+      <c r="R190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="191" hidden="true">
+      <c r="A191" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="D191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E191" s="2"/>
+      <c r="F191" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G191" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J191" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K191" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L191" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="M191" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N191" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q191" s="2"/>
+      <c r="R191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE191" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF191" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="192" hidden="true">
+      <c r="A192" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="P192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q192" s="2"/>
+      <c r="R192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="193" hidden="true">
+      <c r="A193" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K193" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="P193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q193" s="2"/>
+      <c r="R193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="194" hidden="true">
+      <c r="A194" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="P194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ182">
+  <autoFilter ref="A1:AJ194">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21514,7 +22828,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI181">
+  <conditionalFormatting sqref="A2:AI193">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-spezifische-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
